--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 06:24</t>
+          <t>2026-10-25 12:22</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:22</t>
+          <t>2026-10-25 18:19</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 18:19</t>
+          <t>2026-10-26 00:29</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 00:29</t>
+          <t>2026-10-26 06:32</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 06:32</t>
+          <t>2026-10-26 14:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
+          <t>AMARILLO, SALMON, AZUL, LILA</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
+          <t>TOTTO, WINNE POOH</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
+          <t>DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -5536,11 +5536,11 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/2i5ai5chp2u_1784991743787.jpg</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
+          <t>ROJA, NEGRO, BLANCO HUESO</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -6210,11 +6210,11 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lm6eiuewqld_1791399520169.webp</t>
         </is>
       </c>
       <c r="P90" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 14:34</t>
+          <t>2026-10-26 18:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 18:34</t>
+          <t>2026-10-27 00:27</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:27</t>
+          <t>2026-10-27 06:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 06:30</t>
+          <t>2026-10-27 12:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 12:33</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-28 00:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 00:35</t>
+          <t>2026-10-28 06:36</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 06:36</t>
+          <t>2026-10-28 12:37</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1004165238, 1004165237, 1004165236, 1004165235, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165229, 1004165228, 1004165227, 1004165226, 1004165225, 1004165224, 1004165218</t>
+          <t>1004165237, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165227, 1004165226, 1004165224, 1004165218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/j7a765w02fc_1792168079354.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g3gm0hniit5_1792168080708.webp</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3249,7 +3249,11 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="n">
         <v>25000</v>
       </c>
@@ -3270,7 +3274,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>CINAMORROL, CERDITO, AVOCADO, STICH, BLANCA NIEVES, BOB ESPONJA, CAPIBARA, GUERRERAS KPOP, GATA MARIE, LILO Y STICH, PERRO MORADO, OSITA GLOBOS</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
@@ -6660,7 +6668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6671,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 12:37</t>
+          <t>2026-10-28 18:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 18:35</t>
+          <t>2026-10-29 00:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:35</t>
+          <t>2026-10-29 06:38</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 06:38</t>
+          <t>2026-10-29 12:38</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 12:38</t>
+          <t>2026-10-29 18:38</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 18:38</t>
+          <t>2026-10-30 00:36</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -4774,17 +4774,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SET104</t>
+          <t>STP-002</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT TIRA PLUS</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
@@ -4820,37 +4820,37 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
+          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
+          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>STP-002</t>
+          <t>SET104</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
@@ -4886,21 +4886,21 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -6228,17 +6228,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
+          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STU-001</t>
+          <t>SHD-001</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA</t>
+          <t>SHORT TIRA MUNDIALISTA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Única, Plus, Oversize</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -6274,37 +6274,37 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
+          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
+          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SHD-001</t>
+          <t>STU-001</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA MUNDIALISTA</t>
+          <t>SHORT TIRA</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -6340,21 +6340,21 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:36</t>
+          <t>2026-10-30 06:39</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 06:39</t>
+          <t>2026-10-30 12:38</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 12:38</t>
+          <t>2026-10-30 12:54</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 12:54</t>
+          <t>2026-10-30 18:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6274,7 +6274,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
+          <t>OSO LOTSO, MICKEY, TIGERS, AVOCADO, CERDITO, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 18:35</t>
+          <t>2026-10-31 00:41</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 00:41</t>
+          <t>2026-10-31 06:37</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 06:37</t>
+          <t>2026-10-31 12:34</t>
         </is>
       </c>
     </row>
